--- a/ceo_data.xlsx
+++ b/ceo_data.xlsx
@@ -437,11 +437,11 @@
   <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="31" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -1076,7 +1076,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1094,9 +1094,9 @@
           <t>1,560</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1180,7 +1180,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1198,9 +1198,9 @@
           <t>382,894</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Koji Sato</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1250,9 +1250,9 @@
           <t>380,793</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>koji.sato@corporate.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1284,7 +1284,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1302,9 +1302,9 @@
           <t>48,000</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1388,7 +1388,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1406,9 +1406,9 @@
           <t>44,000</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1458,9 +1458,9 @@
           <t>12,479</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1492,7 +1492,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Ron Vachris</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1510,9 +1510,9 @@
           <t>316,000</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>ron.vachris@corporate.com</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1544,7 +1544,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Jamie Dimon</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1562,9 +1562,9 @@
           <t>309,926</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>jamie.dimon@corporate.com</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1718,9 +1718,9 @@
           <t>36,000</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1804,7 +1804,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1822,9 +1822,9 @@
           <t>47,520</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1856,7 +1856,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Carlos Tavares</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1874,9 +1874,9 @@
           <t>258,275</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>carlos.tavares@corporate.com</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Michael Wirth</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1926,9 +1926,9 @@
           <t>45,600</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>michael.wirth@corporate.com</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1978,9 +1978,9 @@
           <t>376,871</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2012,7 +2012,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Han Jong-hee</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2030,9 +2030,9 @@
           <t>267,860</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>han.jong-hee@corporate.com</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2064,7 +2064,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>David Cordani</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2082,9 +2082,9 @@
           <t>71,413</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>david.cordani@corporate.com</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2134,9 +2134,9 @@
           <t>451,003</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2168,7 +2168,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2186,9 +2186,9 @@
           <t>595,000</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2220,7 +2220,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2238,9 +2238,9 @@
           <t>314,149</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2272,7 +2272,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2290,9 +2290,9 @@
           <t>160,000</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2324,7 +2324,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Jim Farley</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2342,9 +2342,9 @@
           <t>177,000</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>jim.farley@corporate.com</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2376,7 +2376,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2394,9 +2394,9 @@
           <t>306,931</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2428,7 +2428,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Mary Barra</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2446,9 +2446,9 @@
           <t>163,000</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>mary.barra@corporate.com</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2480,7 +2480,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2498,9 +2498,9 @@
           <t>104,900</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2532,7 +2532,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2550,9 +2550,9 @@
           <t>154,950</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2584,7 +2584,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2602,9 +2602,9 @@
           <t>166,056</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2688,7 +2688,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2706,9 +2706,9 @@
           <t>336,433</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2740,7 +2740,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2758,9 +2758,9 @@
           <t>258,697</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2810,9 +2810,9 @@
           <t>237,925</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2844,7 +2844,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2862,9 +2862,9 @@
           <t>China</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2896,7 +2896,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2914,9 +2914,9 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3000,7 +3000,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3014,9 +3014,9 @@
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3048,7 +3048,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Unknown CEO</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3066,9 +3066,9 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Contact Pending</t>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3108,7 +3108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3698,27 +3698,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Satya Nadella</t>
+          <t>Koji Sato</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Information technology</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>228,000</t>
+          <t>380,793</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>satya.nadella@corporate.com</t>
+          <t>koji.sato@corporate.com</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Microsoft%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Toyota%20CEO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3750,27 +3750,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Patrick Pouyanné</t>
+          <t>Satya Nadella</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oil and gas</t>
+          <t>Information technology</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>102,579</t>
+          <t>228,000</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>patrick.pouyanné@corporate.com</t>
+          <t>satya.nadella@corporate.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=TotalEnergies%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Microsoft%20CEO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>281</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3802,27 +3802,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gary Nagle</t>
+          <t>Ron Vachris</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Glencore</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>83,426</t>
+          <t>316,000</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>gary.nagle@corporate.com</t>
+          <t>ron.vachris@corporate.com</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Glencore%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Costco%20CEO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3854,27 +3854,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Murray Auchincloss</t>
+          <t>Jamie Dimon</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oil and gas</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>79,400</t>
+          <t>309,926</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>murray.auchincloss@corporate.com</t>
+          <t>jamie.dimon@corporate.com</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=BP%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=JPMorgan Chase%20CEO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3906,27 +3906,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg</t>
+          <t>Patrick Pouyanné</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Social media</t>
+          <t>Oil and gas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>78,450</t>
+          <t>102,579</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>mark.zuckerberg@corporate.com</t>
+          <t>patrick.pouyanné@corporate.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Meta Platforms%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=TotalEnergies%20CEO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3958,50 +3958,518 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Gary Nagle</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Glencore</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>83,426</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>gary.nagle@corporate.com</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Glencore%20CEO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Murray Auchincloss</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BP</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Oil and gas</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>79,400</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>murray.auchincloss@corporate.com</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=BP%20CEO</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Carlos Tavares</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>258,275</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>carlos.tavares@corporate.com</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Stellantis%20CEO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Michael Wirth</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Oil and gas</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>45,600</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>michael.wirth@corporate.com</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Chevron%20CEO</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Han Jong-hee</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>267,860</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>han.jong-hee@corporate.com</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Samsung Electronics%20CEO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>David Cordani</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cigna</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>71,413</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>david.cordani@corporate.com</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Cigna%20CEO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jim Farley</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>177,000</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>jim.farley@corporate.com</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Ford Motor Company%20CEO</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Mary Barra</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>General Motors</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>163,000</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>mary.barra@corporate.com</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=General Motors%20CEO</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mark Zuckerberg</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Social media</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>78,450</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>mark.zuckerberg@corporate.com</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Meta Platforms%20CEO</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Hou Qijun</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>China National Petroleum Corporation</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>476</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>hou.qijun@corporate.com</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/all/?keywords=China National Petroleum Corporation%20CEO</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Billionaire Status</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
         </is>

--- a/ceo_data.xlsx
+++ b/ceo_data.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -445,7 +445,7 @@
     <col width="31" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -660,27 +660,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Amin H. Nasser</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saudi Aramco</t>
+          <t>Randstad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oil and gas</t>
+          <t>Diemen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>73,311</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>amin.h..nasser@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Saudi Aramco%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Randstad%20CEO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -700,39 +700,39 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>0491#491</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tim Cook</t>
+          <t>Amin H. Nasser</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Saudi Aramco</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Information technology</t>
+          <t>Oil and gas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>166,000</t>
+          <t>73,311</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>tim.cook@corporate.com</t>
+          <t>amin.h..nasser@corporate.com</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Apple%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Saudi Aramco%20CEO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>480</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -764,27 +764,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sundar Pichai</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Information technology</t>
+          <t>Chertsey</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>190,820</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>sundar.pichai@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Alphabet%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Compass Group%20CEO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -804,39 +804,39 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>0469#398</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Andrew Witty</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Adecco Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>400,000</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>andrew.witty@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=UnitedHealth Group%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Adecco Group%20CEO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -856,39 +856,39 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>441</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Warren Buffett</t>
+          <t>Tim Cook</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information technology</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>392,400</t>
+          <t>166,000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>warren.buffett@corporate.com</t>
+          <t>tim.cook@corporate.com</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Berkshire Hathaway%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Apple%20CEO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>416</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -920,27 +920,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Karen S. Lynch</t>
+          <t>Sundar Pichai</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>259,500</t>
+          <t>190,820</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>karen.s..lynch@corporate.com</t>
+          <t>sundar.pichai@corporate.com</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=CVS Health%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Alphabet%20CEO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>402</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -972,27 +972,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Oliver Blume</t>
+          <t>Andrew Witty</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Volkswagen Group</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>684,025</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>oliver.blume@corporate.com</t>
+          <t>andrew.witty@corporate.com</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Volkswagen Group%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=UnitedHealth Group%20CEO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1024,27 +1024,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Darren Woods</t>
+          <t>Warren Buffett</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oil and gas</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>61,500</t>
+          <t>392,400</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>darren.woods@corporate.com</t>
+          <t>warren.buffett@corporate.com</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=ExxonMobil%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Berkshire Hathaway%20CEO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>371</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1076,27 +1076,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Karen S. Lynch</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vitol</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1,560</t>
+          <t>259,500</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>karen.s..lynch@corporate.com</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Vitol%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=CVS Health%20CEO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1128,27 +1128,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Wael Sawan</t>
+          <t>Oliver Blume</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Volkswagen Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oil and gas</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>103,000</t>
+          <t>684,025</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>wael.sawan@corporate.com</t>
+          <t>oliver.blume@corporate.com</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Shell%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Volkswagen Group%20CEO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>348</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1180,27 +1180,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Darren Woods</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>China State Construction Engineering</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Oil and gas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>382,894</t>
+          <t>61,500</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>darren.woods@corporate.com</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=China State Construction Engineering%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=ExxonMobil%20CEO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>344</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1232,27 +1232,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Koji Sato</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>Vitol</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>380,793</t>
+          <t>1,560</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>koji.sato@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Toyota%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Vitol%20CEO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1284,27 +1284,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Wael Sawan</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Oil and gas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48,000</t>
+          <t>103,000</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>wael.sawan@corporate.com</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=McKesson%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Shell%20CEO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>323</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1336,27 +1336,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Satya Nadella</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>China State Construction Engineering</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Information technology</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>228,000</t>
+          <t>382,894</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>satya.nadella@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Microsoft%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China State Construction Engineering%20CEO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>320</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Koji Sato</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>380,793</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>koji.sato@corporate.com</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Cencora%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Toyota%20CEO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1445,17 +1445,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trafigura</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12,479</t>
+          <t>48,000</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Trafigura%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=McKesson%20CEO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1492,27 +1492,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ron Vachris</t>
+          <t>Satya Nadella</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Costco</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Information technology</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>316,000</t>
+          <t>228,000</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ron.vachris@corporate.com</t>
+          <t>satya.nadella@corporate.com</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Costco%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Microsoft%20CEO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>281</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1544,27 +1544,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jamie Dimon</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>309,926</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>jamie.dimon@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=JPMorgan Chase%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Cencora%20CEO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>262</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1596,27 +1596,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Patrick Pouyanné</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Oil and gas</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>102,579</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>patrick.pouyanné@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=TotalEnergies%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=American Airlines%20CEO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1636,24 +1636,24 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gary Nagle</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Glencore</t>
+          <t>Trafigura</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>83,426</t>
+          <t>12,479</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>gary.nagle@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Glencore%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Trafigura%20CEO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>244</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1700,27 +1700,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Ron Vachris</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>36,000</t>
+          <t>316,000</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>ron.vachris@corporate.com</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Nvidia%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Costco%20CEO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1752,27 +1752,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Murray Auchincloss</t>
+          <t>Jamie Dimon</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oil and gas</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>79,400</t>
+          <t>309,926</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>murray.auchincloss@corporate.com</t>
+          <t>jamie.dimon@corporate.com</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=BP%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=JPMorgan Chase%20CEO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1809,17 +1809,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47,520</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Cardinal Health%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Caterpillar%20CEO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1844,39 +1844,39 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Carlos Tavares</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Saint-Gobain</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>258,275</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>carlos.tavares@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Stellantis%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Saint-Gobain%20CEO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Michael Wirth</t>
+          <t>Patrick Pouyanné</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45,600</t>
+          <t>102,579</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>michael.wirth@corporate.com</t>
+          <t>patrick.pouyanné@corporate.com</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Chevron%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=TotalEnergies%20CEO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>218</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1960,27 +1960,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Gary Nagle</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>China Construction Bank</t>
+          <t>Glencore</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>376,871</t>
+          <t>83,426</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>gary.nagle@corporate.com</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=China Construction Bank%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Glencore%20CEO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2012,27 +2012,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Han Jong-hee</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>267,860</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>han.jong-hee@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Samsung Electronics%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=HCA Healthcare%20CEO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2052,39 +2052,39 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>David Cordani</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cigna</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>71,413</t>
+          <t>36,000</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>david.cordani@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Cigna%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Nvidia%20CEO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>215</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2116,27 +2116,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Murray Auchincloss</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Agricultural Bank of China</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Oil and gas</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>451,003</t>
+          <t>79,400</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>murray.auchincloss@corporate.com</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Agricultural Bank of China%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=BP%20CEO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2173,17 +2173,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Schwarz Gruppe</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>595,000</t>
+          <t>47,520</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Schwarz Gruppe%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Cardinal Health%20CEO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2220,27 +2220,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Carlos Tavares</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>China Railway Engineering Corporation</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>314,149</t>
+          <t>258,275</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>carlos.tavares@corporate.com</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=China Railway Engineering Corporation%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Stellantis%20CEO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2272,27 +2272,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Michael Wirth</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Conglomerate</t>
+          <t>Oil and gas</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>160,000</t>
+          <t>45,600</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>michael.wirth@corporate.com</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Cargill%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Chevron%20CEO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2324,27 +2324,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jim Farley</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>China Construction Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>177,000</t>
+          <t>376,871</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>jim.farley@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Ford Motor Company%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China Construction Bank%20CEO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>199</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2376,27 +2376,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Han Jong-hee</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bank of China</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>306,931</t>
+          <t>267,860</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>han.jong-hee@corporate.com</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Bank of China%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Samsung Electronics%20CEO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>198</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2428,27 +2428,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mary Barra</t>
+          <t>David Cordani</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>General Motors</t>
+          <t>Cigna</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>71,413</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>mary.barra@corporate.com</t>
+          <t>david.cordani@corporate.com</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=General Motors%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Cigna%20CEO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>195</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2485,17 +2485,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Agricultural Bank of China</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>104,900</t>
+          <t>451,003</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Elevance Health%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Agricultural Bank of China%20CEO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>192</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2537,17 +2537,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BMW Group</t>
+          <t>Schwarz Gruppe</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>154,950</t>
+          <t>595,000</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=BMW Group%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Schwarz Gruppe%20CEO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>180</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>China Railway Engineering Corporation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Automotive</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>166,056</t>
+          <t>314,149</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Mercedes-Benz Group%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China Railway Engineering Corporation%20CEO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>178</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2636,27 +2636,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Social media</t>
+          <t>Conglomerate</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>78,450</t>
+          <t>160,000</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>mark.zuckerberg@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Meta Platforms%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Cargill%20CEO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>177</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2688,27 +2688,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Jim Farley</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>China Railway Construction Corporation</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>336,433</t>
+          <t>177,000</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>jim.farley@corporate.com</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=China Railway Construction Corporation%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Ford Motor Company%20CEO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>176</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2745,17 +2745,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Baowu</t>
+          <t>Bank of China</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>258,697</t>
+          <t>306,931</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Baowu%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Bank of China%20CEO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>172</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2797,17 +2797,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>237,925</t>
+          <t>104,900</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Citigroup%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Elevance Health%20CEO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>171</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2844,27 +2844,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Search Result (Demo)</t>
+          <t>Mary Barra</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Industrial and Commercial Bank of China</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>163,000</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>search.result.(demo)@corporate.com</t>
+          <t>mary.barra@corporate.com</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Industrial and Commercial Bank of China%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=General Motors%20CEO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>171</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Anheuser-Busch InBev</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=Bank of America%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Anheuser-Busch InBev%20CEO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2936,39 +2936,39 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>170</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Hou Qijun</t>
+          <t>Search Result (Demo)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>China National Petroleum Corporation</t>
+          <t>BMW Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>Automotive</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>154,950</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>hou.qijun@corporate.com</t>
+          <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=China National Petroleum Corporation%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=BMW Group%20CEO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>168</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3005,15 +3005,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>China Petrochemical Corporation</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>166,056</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>search.result.(demo)@corporate.com</t>
@@ -3026,7 +3030,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/all/?keywords=China Petrochemical Corporation%20CEO</t>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Mercedes-Benz Group%20CEO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3036,7 +3040,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>165</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3048,52 +3052,2648 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>Mark Zuckerberg</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Social media</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>78,450</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>mark.zuckerberg@corporate.com</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Meta Platforms%20CEO</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Search Result (Demo)</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Disney</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Burbank</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Disney%20CEO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0161#176</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>China Railway Construction Corporation</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>336,433</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China Railway Construction Corporation%20CEO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Baowu</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>258,697</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Baowu%20CEO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Citigroup</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>237,925</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Citigroup%20CEO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Procter &amp; Gamble%20CEO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0154#149</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>China North Industries Group</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China North Industries Group%20CEO</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0146#147</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Walt Disney</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Burbank</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Walt Disney%20CEO</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0145#131</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Christian Dior</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Christian Dior%20CEO</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0143#119</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BASF</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ludwigshafen</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=BASF%20CEO</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0126#143</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Nippon Life Insurance</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Nippon Life Insurance%20CEO</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>DuPont</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Wilmington</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=DuPont%20CEO</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0126#100</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hengli Group</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Suzhou</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Hengli Group%20CEO</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0123#81</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Mark Zuckerberg</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>China Minmetals</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>mark.zuckerberg@corporate.com</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China Minmetals%20CEO</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0120#112</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Amer International Group</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Amer International Group%20CEO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0120#91</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Nestlé</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Vevey</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Nestlé%20CEO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0098#98</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Archer Daniels Midland</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Archer Daniels Midland%20CEO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>0098#98</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=IBM%20CEO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>China Post Group</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China Post Group%20CEO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>0086#83</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Nestle</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Nestle%20CEO</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>China Mobile Communications</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China Mobile Communications%20CEO</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>0062#55</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Boeing%20CEO</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>0060#68</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Leiden</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Airbus%20CEO</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>0060#116</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Kroger</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Kroger%20CEO</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0058#51</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Industrial and Commercial Bank of China</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Industrial and Commercial Bank of China%20CEO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Gazprom</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Gazprom%20CEO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Walgreens Boots Alliance</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Deerfield</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Walgreens Boots Alliance%20CEO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>0045#45</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>China Baowu Steel Group</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China Baowu Steel Group%20CEO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>0044#44</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Sinochem Holdings</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Sinochem Holdings%20CEO</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>0038#54</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=AT&amp;T%20CEO</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0032#32</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Sinochem Holdings [zh]</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Sinochem Holdings [zh]%20CEO</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0031#31</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Siemens%20CEO</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>0031#74</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>General Electric</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=General Electric%20CEO</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>0031#48</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>AXA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=AXA%20CEO</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Bank of America%20CEO</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>26.5</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Industrial &amp; Commercial Bank</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Industrial &amp; Commercial Bank%20CEO</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Hou Qijun</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>China National Petroleum Corporation</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>hou.qijun@corporate.com</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China National Petroleum Corporation%20CEO</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>25.2</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>China Construction Engineering</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China Construction Engineering%20CEO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EXOR Group</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=EXOR Group%20CEO</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Trafigura Group</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Trafigura Group%20CEO</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>0012#19</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>McKesson Corporation</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=McKesson Corporation%20CEO</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>0011#13</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>China Petrochemical Corporation</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China Petrochemical Corporation%20CEO</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
         <is>
           <t>Foxconn</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>search.result.(demo)@corporate.com</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/all/?keywords=Foxconn%20CEO</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Billionaire Status</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Oliver Blume</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Volkswagen</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>oliver.blume@corporate.com</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Volkswagen%20CEO</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Hou Qijun</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>China National Petroleum</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>hou.qijun@corporate.com</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China National Petroleum%20CEO</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Petroleum</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Zhang Zhigang</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>State Grid</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>zhang.zhigang@corporate.com</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=State Grid%20CEO</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Ma Yongsheng</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Sinopec Group</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>ma.yongsheng@corporate.com</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Sinopec Group%20CEO</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Petroleum</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Search Result (Demo)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Exxon Mobil</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>search.result.(demo)@corporate.com</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Exxon Mobil%20CEO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Petroleum</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Koji Sato</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Toyota Motor</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>koji.sato@corporate.com</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Toyota Motor%20CEO</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Wael Sawan</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Royal Dutch Shell</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Netherlands / United Kingdom</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>wael.sawan@corporate.com</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Royal Dutch Shell%20CEO</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Petroleum</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Andy Jassy</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Amazon.com</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>andy.jassy@corporate.com</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Amazon.com%20CEO</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Internet Services and Retailing</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
         </is>
       </c>
     </row>
@@ -3108,7 +5708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3119,7 +5719,7 @@
     <col width="31" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4426,52 +7026,468 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Mark Zuckerberg</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>China Minmetals</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>mark.zuckerberg@corporate.com</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China Minmetals%20CEO</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0120#112</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Hou Qijun</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>China National Petroleum Corporation</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>476</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>hou.qijun@corporate.com</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/all/?keywords=China National Petroleum Corporation%20CEO</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Billionaire Status</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>25.2</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/List_of_largest_companies_by_revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Oliver Blume</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Volkswagen</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>oliver.blume@corporate.com</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Volkswagen%20CEO</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Hou Qijun</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>China National Petroleum</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>hou.qijun@corporate.com</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=China National Petroleum%20CEO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Petroleum</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Zhang Zhigang</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>State Grid</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>zhang.zhigang@corporate.com</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=State Grid%20CEO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ma Yongsheng</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sinopec Group</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>ma.yongsheng@corporate.com</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Sinopec Group%20CEO</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Petroleum</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Koji Sato</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Toyota Motor</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>koji.sato@corporate.com</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Toyota Motor%20CEO</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Wael Sawan</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Royal Dutch Shell</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Netherlands / United Kingdom</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>wael.sawan@corporate.com</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Royal Dutch Shell%20CEO</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Petroleum</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Andy Jassy</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Amazon.com</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>andy.jassy@corporate.com</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>+1-XXX-XXX-XXXX (Switchboard)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/all/?keywords=Amazon.com%20CEO</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Billionaire Status</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Internet Services and Retailing</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Fortune_Global_500</t>
         </is>
       </c>
     </row>
